--- a/AAII_Financials/Quarterly/MCHB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCHB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="92">
   <si>
     <t>MCHB</t>
   </si>
@@ -656,59 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -727,31 +729,34 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E8" s="3">
         <v>192300</v>
       </c>
-      <c r="E8" s="3">
-        <v>227000</v>
-      </c>
       <c r="F8" s="3">
+        <v>228000</v>
+      </c>
+      <c r="G8" s="3">
         <v>119000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>150100</v>
+      </c>
+      <c r="I8" s="3">
         <v>147100</v>
       </c>
-      <c r="H8" s="3">
-        <v>151200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>141100</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>151100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -774,8 +779,11 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -821,35 +829,38 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E10" s="3">
         <v>192300</v>
       </c>
-      <c r="E10" s="3">
-        <v>227000</v>
-      </c>
       <c r="F10" s="3">
+        <v>228000</v>
+      </c>
+      <c r="G10" s="3">
         <v>119000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>150100</v>
+      </c>
+      <c r="I10" s="3">
         <v>147100</v>
       </c>
-      <c r="H10" s="3">
-        <v>151200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>141100</v>
-      </c>
       <c r="J10" s="3">
+        <v>151100</v>
+      </c>
+      <c r="K10" s="3">
         <v>-69200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,8 +879,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +901,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,8 +949,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -981,29 +999,32 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E14" s="3">
         <v>4800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-51600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-26500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,40 +1049,43 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E15" s="3">
         <v>12400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I15" s="3">
         <v>5100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>5100</v>
       </c>
-      <c r="I15" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1075,8 +1099,11 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1091,35 +1118,36 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E17" s="3">
         <v>115000</v>
       </c>
-      <c r="E17" s="3">
-        <v>115600</v>
-      </c>
       <c r="F17" s="3">
+        <v>116600</v>
+      </c>
+      <c r="G17" s="3">
         <v>93600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>80500</v>
+      </c>
+      <c r="I17" s="3">
         <v>77700</v>
       </c>
-      <c r="H17" s="3">
-        <v>74700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>79200</v>
-      </c>
       <c r="J17" s="3">
+        <v>74600</v>
+      </c>
+      <c r="K17" s="3">
         <v>81300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,35 +1166,38 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E18" s="3">
         <v>77300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>111500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>69700</v>
+      </c>
+      <c r="I18" s="3">
         <v>69400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>76500</v>
       </c>
-      <c r="I18" s="3">
-        <v>61900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-150500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1185,8 +1216,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1204,35 +1238,36 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E20" s="3">
         <v>10600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I20" s="3">
         <v>7600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>9300</v>
       </c>
-      <c r="I20" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6900</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1251,40 +1286,43 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E21" s="3">
         <v>79100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>115900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>69600</v>
+      </c>
+      <c r="I21" s="3">
         <v>66900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>72300</v>
       </c>
-      <c r="I21" s="3">
-        <v>61000</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-151600</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
@@ -1298,8 +1336,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1345,35 +1386,38 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E23" s="3">
         <v>61900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>154000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>59000</v>
+      </c>
+      <c r="I23" s="3">
         <v>61500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>67200</v>
       </c>
-      <c r="I23" s="3">
-        <v>55500</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-157400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1392,35 +1436,38 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E24" s="3">
         <v>17800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-10100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I24" s="3">
         <v>17700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>15500</v>
       </c>
-      <c r="I24" s="3">
-        <v>15500</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-44100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,8 +1486,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1486,35 +1536,38 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E26" s="3">
         <v>44100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>124300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>55200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>42500</v>
+      </c>
+      <c r="I26" s="3">
         <v>43800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>51700</v>
       </c>
-      <c r="I26" s="3">
-        <v>39900</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-113300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1533,35 +1586,38 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E27" s="3">
         <v>44100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>124300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>55200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>42500</v>
+      </c>
+      <c r="I27" s="3">
         <v>43800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>51700</v>
       </c>
-      <c r="I27" s="3">
-        <v>39900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-113300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1636,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1627,8 +1686,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1659,8 +1721,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
@@ -1674,8 +1736,11 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1721,8 +1786,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1768,35 +1836,38 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-7600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-9300</v>
       </c>
-      <c r="I32" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6900</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1815,35 +1886,38 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E33" s="3">
         <v>44100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>124300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>55200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>42500</v>
+      </c>
+      <c r="I33" s="3">
         <v>43800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>51700</v>
       </c>
-      <c r="I33" s="3">
-        <v>39900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-113300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,8 +1936,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1909,35 +1986,38 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E35" s="3">
         <v>44100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>124300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>55200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>42500</v>
+      </c>
+      <c r="I35" s="3">
         <v>43800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>51700</v>
       </c>
-      <c r="I35" s="3">
-        <v>39900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-113300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1956,40 +2036,43 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2091,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2027,8 +2113,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2046,32 +2133,33 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>553900</v>
+      </c>
+      <c r="E41" s="3">
         <v>483500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1030000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1442600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>2079000</v>
+      </c>
+      <c r="I41" s="3">
         <v>798300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>999700</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,40 +2181,43 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E42" s="3">
         <v>53300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>53700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>12800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2140,8 +2231,11 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2187,32 +2281,35 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E44" s="3">
         <v>4700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>13400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>15600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,32 +2331,35 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E45" s="3">
         <v>51700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>53100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>414000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3">
+        <v>47700</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>33600</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,32 +2381,35 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>686400</v>
+      </c>
+      <c r="E46" s="3">
         <v>597900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1147700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1963700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>2134200</v>
+      </c>
+      <c r="I46" s="3">
         <v>811900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1062300</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,32 +2431,35 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5545600</v>
+      </c>
+      <c r="E47" s="3">
         <v>5384600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5390600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4871400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>3984000</v>
+      </c>
+      <c r="I47" s="3">
         <v>5020500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>4537600</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2375,32 +2481,35 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>216200</v>
+      </c>
+      <c r="E48" s="3">
         <v>221200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>226000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>229600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>171400</v>
+      </c>
+      <c r="I48" s="3">
         <v>171800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>170900</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2422,34 +2531,37 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1000400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1132600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1141600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1075200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>876600</v>
+      </c>
+      <c r="I49" s="3">
         <v>879300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>882000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2469,8 +2581,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2516,8 +2631,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2563,32 +2681,35 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>357700</v>
+      </c>
+      <c r="E52" s="3">
         <v>356100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>346200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>169200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>233500</v>
+      </c>
+      <c r="I52" s="3">
         <v>316300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>230700</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,8 +2731,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2657,32 +2781,35 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21230800</v>
+      </c>
+      <c r="E54" s="3">
         <v>21389000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22351500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22708800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>16571200</v>
+      </c>
+      <c r="I54" s="3">
         <v>16540300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16490100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,8 +2831,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2723,8 +2853,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2742,32 +2873,33 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18089400</v>
+      </c>
+      <c r="E57" s="3">
         <v>18242800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19025000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19452800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>13968900</v>
+      </c>
+      <c r="I57" s="3">
         <v>13986200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13941800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,34 +2921,37 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E58" s="3">
         <v>137200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>99200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>75000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>11100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2836,13 +2971,16 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>6000</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -2883,32 +3021,35 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18326200</v>
+      </c>
+      <c r="E60" s="3">
         <v>18507900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19284000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19718400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>14095300</v>
+      </c>
+      <c r="I60" s="3">
         <v>14107300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14110200</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,40 +3071,43 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>208600</v>
+      </c>
+      <c r="E61" s="3">
         <v>82400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>188200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>216300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>59200</v>
+      </c>
+      <c r="I61" s="3">
         <v>58900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>56100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3" t="s">
-        <v>3</v>
+      <c r="M61" s="3">
+        <v>0</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>3</v>
@@ -2977,17 +3121,20 @@
       <c r="Q61" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7300</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,8 +3171,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3071,8 +3221,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3118,8 +3271,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3165,32 +3321,35 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18540900</v>
+      </c>
+      <c r="E66" s="3">
         <v>18597600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19489100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19934700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>14154600</v>
+      </c>
+      <c r="I66" s="3">
         <v>14166200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14188200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3212,8 +3371,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3231,8 +3393,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3278,8 +3441,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3325,8 +3491,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3357,8 +3526,8 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
+      <c r="M70" s="3">
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>3</v>
@@ -3372,8 +3541,11 @@
       <c r="Q70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3419,32 +3591,35 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E72" s="3">
         <v>407900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>456700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>381000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>325800</v>
+      </c>
+      <c r="I72" s="3">
         <v>283300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>239500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3641,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3513,8 +3691,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3560,8 +3741,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3607,35 +3791,38 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2689900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2791400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2862400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2774100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>2416600</v>
+      </c>
+      <c r="I76" s="3">
         <v>2374100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2301900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2235600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3654,8 +3841,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3701,40 +3891,43 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3753,35 +3946,38 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E81" s="3">
         <v>44100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>124300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>55200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>42500</v>
+      </c>
+      <c r="I81" s="3">
         <v>43800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>51700</v>
       </c>
-      <c r="I81" s="3">
-        <v>39900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-113300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,8 +3996,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3819,26 +4018,27 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F83" s="3">
         <v>2300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2100</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +4066,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3913,8 +4116,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3960,8 +4166,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4007,8 +4216,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4054,8 +4266,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4101,35 +4316,38 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E89" s="3">
         <v>11400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>113900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>65100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>74900</v>
       </c>
-      <c r="I89" s="3">
-        <v>70500</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>61300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4148,8 +4366,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4167,35 +4388,36 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,8 +4436,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4261,8 +4486,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4308,35 +4536,38 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E94" s="3">
         <v>381800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-50400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>607500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>1232900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-244400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-79400</v>
       </c>
-      <c r="I94" s="3">
-        <v>54900</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>357200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4586,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4374,35 +4608,36 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E96" s="3">
         <v>92600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>48600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>30000</v>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>65000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
@@ -4421,8 +4656,11 @@
       <c r="Q96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4468,8 +4706,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4515,8 +4756,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4562,35 +4806,38 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-235200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-939700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-476200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1259800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="I100" s="3">
         <v>44400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-174000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-790100</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4609,8 +4856,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4656,40 +4906,43 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-546500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-412700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-636300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>1280700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-201400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-178500</v>
       </c>
-      <c r="I102" s="3">
-        <v>-664700</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>218300</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4701,6 +4954,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
